--- a/astro-site/public/dl/seafood-restaurant-checklist-templates/06-seafood-restaurant-duties-by-role.xlsx
+++ b/astro-site/public/dl/seafood-restaurant-checklist-templates/06-seafood-restaurant-duties-by-role.xlsx
@@ -808,7 +808,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Cook fish: oven, griddle, grill, steam, fried</t>
+          <t>Cook fish: oven, griddle, grill, steam, fry</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       <c r="E31" s="6" t="inlineStr"/>
       <c r="F31" s="6" t="inlineStr"/>
     </row>
-    <row r="32" ht="20" customHeight="1">
+    <row r="32" ht="41" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Server</t>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Suggest white wines and Albarino pairings (21+ with ID, 23 U.S.C. 158)</t>
+          <t>Suggest white wine pairings (Albariño, Sauvignon Blanc, Muscadet, Chablis; 21+ with ID, 23 U.S.C. 158)</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
